--- a/Documents/Dev-Files/Parts List/Parts List - Revised.xlsx
+++ b/Documents/Dev-Files/Parts List/Parts List - Revised.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\ChrisitanRaun-AnnanasMotor\Documents\Dev-Files\Parts List\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAA1B38C-5A5C-4C78-8063-926CA0F5E16F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6952EE58-20C5-4346-9F2A-E198BB672450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{623B4204-36C6-4A79-936E-19F9F488D703}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="56">
   <si>
     <t>S.No</t>
   </si>
@@ -75,9 +75,6 @@
     <t>Encoder</t>
   </si>
   <si>
-    <t>AEAT-8800-Q24</t>
-  </si>
-  <si>
     <t>Rotary Magentic Encoder</t>
   </si>
   <si>
@@ -108,24 +105,12 @@
     <t>Header</t>
   </si>
   <si>
-    <t>M55-7012042R</t>
-  </si>
-  <si>
     <t>Debugging Header</t>
   </si>
   <si>
     <t>MagJack</t>
   </si>
   <si>
-    <t>Mouser</t>
-  </si>
-  <si>
-    <t>ARM Microcontrollers - MCU XMC4000</t>
-  </si>
-  <si>
-    <t>XMC4700F144K1536AAXQMA1</t>
-  </si>
-  <si>
     <t>HR915310A</t>
   </si>
   <si>
@@ -153,28 +138,61 @@
     <t>CHRISTIAN RAUN COMPONENTS LIST - Revised</t>
   </si>
   <si>
-    <t>LAN8700C-AEZG-TR</t>
-  </si>
-  <si>
-    <t>Ethernet tranceiver</t>
-  </si>
-  <si>
-    <t>Newark</t>
-  </si>
-  <si>
-    <t>MII/RMII 10/100 ETHERNET TRANSCEIVER 36 VQFN 6X6X1.0MM T/R ROHS COMPLIANT: YES</t>
-  </si>
-  <si>
     <t>Ethernet Connectors/Modular Connectors (RJ45)</t>
   </si>
   <si>
-    <t>IC BUS SWITCH 8 X 1:1 20VQFN</t>
-  </si>
-  <si>
-    <t>SN74CB3Q3245RGYR</t>
-  </si>
-  <si>
-    <t>Level Shifter</t>
+    <t>DC input jack</t>
+  </si>
+  <si>
+    <t>TLE5012BE5000FUMA1</t>
+  </si>
+  <si>
+    <t>DigiKey</t>
+  </si>
+  <si>
+    <t>LAN9255-I/ZMX019</t>
+  </si>
+  <si>
+    <t>IC ETHERCAT SLAVE CONTROLLER</t>
+  </si>
+  <si>
+    <t>SBH11-PBPC-D10-ST-BK</t>
+  </si>
+  <si>
+    <t>for 25 pieces. Price will decrease till $13 when ordered around 200 pieces.</t>
+  </si>
+  <si>
+    <t>ADC-028-1-T/R-PA10T</t>
+  </si>
+  <si>
+    <t>Power Barrel Connector Jack 2.00mm ID (0.079"), 5.50mm OD (0.217") Surface Mount, Right Angle</t>
+  </si>
+  <si>
+    <t>Screw terminals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connector for a 4 wire stepper </t>
+  </si>
+  <si>
+    <t>Drive Mosfets</t>
+  </si>
+  <si>
+    <t>C3E-25.000-8-1015-X-M</t>
+  </si>
+  <si>
+    <t>CRYSTAL 25.0000MHZ 8PF SMD</t>
+  </si>
+  <si>
+    <t>Crystal</t>
+  </si>
+  <si>
+    <t>FDMC86106LZ</t>
+  </si>
+  <si>
+    <t>MOSFET N-CH 100V 3.3A POWER33</t>
+  </si>
+  <si>
+    <t>1-24 pieces</t>
   </si>
 </sst>
 </file>
@@ -184,7 +202,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -204,6 +222,12 @@
       <b/>
       <sz val="12"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -347,63 +371,69 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -412,22 +442,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="12">
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -568,26 +582,42 @@
       </border>
     </dxf>
     <dxf>
-      <border>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -604,15 +634,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{29E9361C-78C2-48C7-891A-B03AA0352AB1}" name="Table2" displayName="Table2" ref="A2:G18" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="10" tableBorderDxfId="11" totalsRowBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{29E9361C-78C2-48C7-891A-B03AA0352AB1}" name="Table2" displayName="Table2" ref="A2:G17" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8" totalsRowBorderDxfId="7">
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{074CA092-EBD3-4E18-B22A-8F972F914B28}" name="S.No" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{18CB7E39-4265-430B-8777-0EE8A4B58655}" name="Component Name" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{45862D11-CD61-46FC-8326-308275CC6DB8}" name="Manufacturer Part Number" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{F992FF51-435A-4C58-AD4C-0699037533E8}" name="Description" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{96C0499C-A0FB-4857-859B-545A4547ABD9}" name="Reference URL" dataDxfId="4" dataCellStyle="Hyperlink"/>
-    <tableColumn id="6" xr3:uid="{F1CAF6DF-B8DC-4E9D-A60A-FD987F5B78D0}" name="Unit Cost" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{8B895613-6226-4609-92A1-19D9B147B311}" name="Remarks from Client" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{074CA092-EBD3-4E18-B22A-8F972F914B28}" name="S.No" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{18CB7E39-4265-430B-8777-0EE8A4B58655}" name="Component Name" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{45862D11-CD61-46FC-8326-308275CC6DB8}" name="Manufacturer Part Number" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{F992FF51-435A-4C58-AD4C-0699037533E8}" name="Description" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{96C0499C-A0FB-4857-859B-545A4547ABD9}" name="Reference URL" dataDxfId="2" dataCellStyle="Hyperlink"/>
+    <tableColumn id="6" xr3:uid="{F1CAF6DF-B8DC-4E9D-A60A-FD987F5B78D0}" name="Unit Cost" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{8B895613-6226-4609-92A1-19D9B147B311}" name="Remarks from Client" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -915,7 +945,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CB0C397-22AD-463F-8CBD-1AF936A9EBA0}">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.5703125" customWidth="1"/>
@@ -928,326 +958,345 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="10">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="3">
+        <v>6.63</v>
+      </c>
+      <c r="G3" s="11"/>
+    </row>
+    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="10">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="9" t="s">
+      <c r="D4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" s="3">
+        <v>16.18</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="10">
         <v>3</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="B5" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0.21</v>
+      </c>
+      <c r="G5" s="11"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="10">
         <v>4</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="B6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0.65</v>
+      </c>
+      <c r="G6" s="11"/>
+    </row>
+    <row r="7" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10">
         <v>5</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="B7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="3">
+        <v>2.46</v>
+      </c>
+      <c r="G7" s="11"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="10">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="11">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="B8" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="G8" s="11"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="10">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="B9" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.43</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="10">
         <v>8</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="B10" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="G10" s="11"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="10">
         <v>9</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="B11" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="4">
-        <v>6.63</v>
-      </c>
-      <c r="G3" s="12"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="11">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="F11" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="G11" s="11"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="10">
+        <v>10</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="3">
+        <v>18.95</v>
+      </c>
+      <c r="G12" s="13"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="10">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="4">
-        <v>16.11</v>
-      </c>
-      <c r="G4" s="12"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="11">
+      <c r="B13" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="3">
+        <v>3.26</v>
+      </c>
+      <c r="G13" s="13"/>
+    </row>
+    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="10">
+        <v>12</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14" s="6">
         <v>3</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="G14" s="11"/>
+    </row>
+    <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="10">
+        <v>13</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="4">
-        <v>0.21</v>
-      </c>
-      <c r="G5" s="12"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="11">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="C15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="G15" s="11"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="10">
         <v>14</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0.65</v>
-      </c>
-      <c r="G6" s="12"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="11">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="4">
-        <v>9.36</v>
-      </c>
-      <c r="G7" s="12"/>
-    </row>
-    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="11">
-        <v>6</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="7">
-        <v>1.82</v>
-      </c>
-      <c r="G8" s="12"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="11">
-        <v>7</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="B16" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1985218</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="4">
-        <v>0.88</v>
-      </c>
-      <c r="G9" s="12"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="11">
-        <v>8</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="4">
-        <v>0.45</v>
-      </c>
-      <c r="G10" s="12"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="11">
-        <v>9</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="4">
-        <v>1.34</v>
-      </c>
-      <c r="G11" s="12"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="11">
-        <v>10</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" s="4">
-        <v>18.95</v>
-      </c>
-      <c r="G12" s="14"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="11">
-        <v>11</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" s="4">
-        <v>3.26</v>
-      </c>
-      <c r="G13" s="14"/>
-    </row>
-    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="11">
-        <v>12</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F14" s="7">
-        <v>3</v>
-      </c>
-      <c r="G14" s="12"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="11"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="12"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="11"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="12"/>
+      <c r="F16" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="G16" s="11"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="11"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="12"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="13"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="14"/>
+      <c r="A17" s="12"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1256,21 +1305,23 @@
   <hyperlinks>
     <hyperlink ref="E3" r:id="rId1" xr:uid="{26C41CE9-6DD4-417E-B327-9FEAF34153CA}"/>
     <hyperlink ref="E6" r:id="rId2" xr:uid="{4A8D8176-DFDF-4BE5-BF45-322C3D4261B7}"/>
-    <hyperlink ref="E7" r:id="rId3" xr:uid="{C32D6C63-BF95-4A72-AB73-55F6E42AD1F4}"/>
-    <hyperlink ref="E12" r:id="rId4" xr:uid="{06A9B98D-F6A0-451E-AE25-7582C35573FF}"/>
-    <hyperlink ref="E13" r:id="rId5" xr:uid="{05EAD26A-0BB8-4F3E-9D94-1A56DC8B5E06}"/>
-    <hyperlink ref="E11" r:id="rId6" xr:uid="{9FB9BE64-1577-475B-9811-D2A2A41C49BD}"/>
-    <hyperlink ref="E4" r:id="rId7" xr:uid="{E31C7531-1F66-4B6E-B4FE-763ED2A60F5E}"/>
-    <hyperlink ref="E14" r:id="rId8" xr:uid="{779ECD78-33EE-49DA-A32E-80F97346C34B}"/>
-    <hyperlink ref="E5" r:id="rId9" xr:uid="{965C0271-F5D8-439C-A055-4223ED6B5930}"/>
-    <hyperlink ref="E8" r:id="rId10" xr:uid="{B5EBF6B2-7A27-4B86-8232-C59C0348C9CD}"/>
-    <hyperlink ref="E10" r:id="rId11" xr:uid="{B32AEC71-2B64-4732-A393-F40A4AD5BD48}"/>
-    <hyperlink ref="E9" r:id="rId12" xr:uid="{C98B57A6-6A31-4966-819A-11BE1CE701CF}"/>
+    <hyperlink ref="E12" r:id="rId3" xr:uid="{06A9B98D-F6A0-451E-AE25-7582C35573FF}"/>
+    <hyperlink ref="E13" r:id="rId4" xr:uid="{05EAD26A-0BB8-4F3E-9D94-1A56DC8B5E06}"/>
+    <hyperlink ref="E4" r:id="rId5" xr:uid="{E31C7531-1F66-4B6E-B4FE-763ED2A60F5E}"/>
+    <hyperlink ref="E14" r:id="rId6" xr:uid="{779ECD78-33EE-49DA-A32E-80F97346C34B}"/>
+    <hyperlink ref="E5" r:id="rId7" xr:uid="{965C0271-F5D8-439C-A055-4223ED6B5930}"/>
+    <hyperlink ref="E10" r:id="rId8" xr:uid="{B32AEC71-2B64-4732-A393-F40A4AD5BD48}"/>
+    <hyperlink ref="E7" r:id="rId9" xr:uid="{C32D6C63-BF95-4A72-AB73-55F6E42AD1F4}"/>
+    <hyperlink ref="E11" r:id="rId10" xr:uid="{9FB9BE64-1577-475B-9811-D2A2A41C49BD}"/>
+    <hyperlink ref="E15" r:id="rId11" xr:uid="{18D7F878-86F5-417E-B342-D1A319A6B4A9}"/>
+    <hyperlink ref="E16" r:id="rId12" xr:uid="{00AA1C19-436A-4F64-AA4E-B82B03414973}"/>
+    <hyperlink ref="E8" r:id="rId13" xr:uid="{9293B878-7405-4DA0-BDE8-47C20655BEB3}"/>
+    <hyperlink ref="E9" r:id="rId14" xr:uid="{AB3A5CA8-FAA3-4E8C-AD4A-596D6E227D3A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId13"/>
+  <pageSetup orientation="portrait" r:id="rId15"/>
   <tableParts count="1">
-    <tablePart r:id="rId14"/>
+    <tablePart r:id="rId16"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Documents/Dev-Files/Parts List/Parts List - Revised.xlsx
+++ b/Documents/Dev-Files/Parts List/Parts List - Revised.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24511"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\ChrisitanRaun-AnnanasMotor\Documents\Dev-Files\Parts List\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\ChrisitanRaun-AnnanasMotor\Documents\Dev-Files\Parts List\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ABE92FA-B946-4FF2-9318-C4C9F492D32F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0003B695-E80F-48FF-8998-67974CAEB08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{623B4204-36C6-4A79-936E-19F9F488D703}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{623B4204-36C6-4A79-936E-19F9F488D703}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,14 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -321,7 +329,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -336,45 +344,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -404,25 +373,91 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color theme="0"/>
+      <top style="medium">
+        <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="thin">
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -431,47 +466,23 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thick">
-        <color theme="0"/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right/>
-      <top style="thick">
-        <color theme="0"/>
+      <top style="thin">
+        <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right/>
-      <top style="thick">
-        <color theme="0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thick">
-        <color theme="0"/>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -480,88 +491,109 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="8" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -878,59 +910,59 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CB0C397-22AD-463F-8CBD-1AF936A9EBA0}">
   <dimension ref="A1:N19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.5703125" customWidth="1"/>
-    <col min="2" max="2" width="26.42578125" customWidth="1"/>
-    <col min="3" max="3" width="24.5703125" customWidth="1"/>
-    <col min="4" max="4" width="28.28515625" customWidth="1"/>
-    <col min="5" max="5" width="40.140625" customWidth="1"/>
-    <col min="6" max="6" width="21.5703125" customWidth="1"/>
+    <col min="1" max="1" width="8.5546875" customWidth="1"/>
+    <col min="2" max="2" width="26.44140625" customWidth="1"/>
+    <col min="3" max="3" width="24.5546875" customWidth="1"/>
+    <col min="4" max="4" width="28.33203125" customWidth="1"/>
+    <col min="5" max="5" width="40.109375" customWidth="1"/>
+    <col min="6" max="6" width="21.5546875" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="43" customWidth="1"/>
+    <col min="8" max="8" width="33.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="4"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="24" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="1"/>
@@ -940,29 +972,29 @@
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
     </row>
-    <row r="3" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+    <row r="3" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="17">
         <v>1</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="29">
         <v>2.2999999999999998</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="30" t="s">
         <v>34</v>
       </c>
       <c r="I3" s="1"/>
@@ -972,27 +1004,27 @@
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
+    <row r="4" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="15">
         <v>2</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="12" t="s">
+      <c r="B4" s="20"/>
+      <c r="C4" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="9">
         <v>14.7</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H4" s="10" t="s">
         <v>35</v>
       </c>
       <c r="I4" s="1"/>
@@ -1002,27 +1034,27 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+    <row r="5" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="17">
         <v>3</v>
       </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="7" t="s">
+      <c r="B5" s="20"/>
+      <c r="C5" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="5">
         <v>0.16</v>
       </c>
-      <c r="H5" s="16"/>
+      <c r="H5" s="11"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
@@ -1030,25 +1062,27 @@
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="12" t="s">
+    <row r="6" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="17">
+        <v>4</v>
+      </c>
+      <c r="B6" s="20"/>
+      <c r="C6" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="9">
         <v>0.5</v>
       </c>
-      <c r="H6" s="17"/>
+      <c r="H6" s="12"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -1056,27 +1090,27 @@
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
-        <v>4</v>
-      </c>
-      <c r="B7" s="25"/>
-      <c r="C7" s="7" t="s">
+    <row r="7" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="17">
+        <v>5</v>
+      </c>
+      <c r="B7" s="20"/>
+      <c r="C7" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="5">
         <v>0.23</v>
       </c>
-      <c r="H7" s="16"/>
+      <c r="H7" s="11"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -1084,27 +1118,27 @@
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
     </row>
-    <row r="8" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="12">
-        <v>5</v>
-      </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="12" t="s">
+    <row r="8" spans="1:14" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="15">
+        <v>6</v>
+      </c>
+      <c r="B8" s="21"/>
+      <c r="C8" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="9">
         <v>2.46</v>
       </c>
-      <c r="H8" s="17"/>
+      <c r="H8" s="12"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -1112,29 +1146,29 @@
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
+    <row r="9" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="17">
+        <v>7</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="G9" s="10">
+      <c r="G9" s="5">
         <v>0.25</v>
       </c>
-      <c r="H9" s="16"/>
+      <c r="H9" s="11"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -1142,25 +1176,27 @@
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
     </row>
-    <row r="10" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="12"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="12" t="s">
+    <row r="10" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="17">
+        <v>8</v>
+      </c>
+      <c r="B10" s="21"/>
+      <c r="C10" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="F10" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="9">
         <v>0.45</v>
       </c>
-      <c r="H10" s="17"/>
+      <c r="H10" s="12"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -1168,30 +1204,30 @@
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
     </row>
-    <row r="11" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
-        <v>7</v>
-      </c>
-      <c r="B11" s="7" t="s">
+    <row r="11" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="17">
+        <v>9</v>
+      </c>
+      <c r="B11" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="5">
         <f>0.1</f>
         <v>0.1</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="6" t="s">
         <v>47</v>
       </c>
       <c r="I11" s="1"/>
@@ -1201,27 +1237,29 @@
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12" t="s">
+    <row r="12" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="17">
+        <v>10</v>
+      </c>
+      <c r="B12" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="9">
         <v>9.2999999999999999E-2</v>
       </c>
-      <c r="H12" s="15"/>
+      <c r="H12" s="10"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -1229,29 +1267,29 @@
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
-        <v>10</v>
-      </c>
-      <c r="B13" s="7" t="s">
+    <row r="13" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="17">
+        <v>11</v>
+      </c>
+      <c r="B13" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="5">
         <v>18.95</v>
       </c>
-      <c r="H13" s="16"/>
+      <c r="H13" s="11"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -1259,29 +1297,29 @@
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
     </row>
-    <row r="14" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="12">
-        <v>11</v>
-      </c>
-      <c r="B14" s="12" t="s">
+    <row r="14" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="15">
+        <v>12</v>
+      </c>
+      <c r="B14" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F14" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="G14" s="14">
+      <c r="G14" s="9">
         <v>1.3</v>
       </c>
-      <c r="H14" s="17"/>
+      <c r="H14" s="12"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -1289,29 +1327,29 @@
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
-        <v>9</v>
-      </c>
-      <c r="B15" s="27" t="s">
+    <row r="15" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="17">
+        <v>13</v>
+      </c>
+      <c r="B15" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="5">
         <v>0.5</v>
       </c>
-      <c r="H15" s="16"/>
+      <c r="H15" s="11"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -1319,28 +1357,28 @@
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
     </row>
-    <row r="16" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="12">
-        <v>12</v>
-      </c>
-      <c r="B16" s="25"/>
-      <c r="C16" s="12" t="s">
+    <row r="16" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="17">
+        <v>14</v>
+      </c>
+      <c r="B16" s="20"/>
+      <c r="C16" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F16" s="13" t="s">
+      <c r="F16" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="9">
         <f>1.1</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="H16" s="17"/>
+      <c r="H16" s="12"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -1348,27 +1386,27 @@
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
-        <v>13</v>
-      </c>
-      <c r="B17" s="25"/>
-      <c r="C17" s="7" t="s">
+    <row r="17" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="17">
+        <v>15</v>
+      </c>
+      <c r="B17" s="20"/>
+      <c r="C17" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="5">
         <v>0.09</v>
       </c>
-      <c r="H17" s="16"/>
+      <c r="H17" s="11"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
@@ -1376,27 +1414,27 @@
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
     </row>
-    <row r="18" spans="1:14" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="12">
-        <v>14</v>
-      </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="19" t="s">
+    <row r="18" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="15">
+        <v>16</v>
+      </c>
+      <c r="B18" s="20"/>
+      <c r="C18" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="F18" s="13" t="s">
+      <c r="F18" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="G18" s="14">
+      <c r="G18" s="9">
         <v>0.156</v>
       </c>
-      <c r="H18" s="17"/>
+      <c r="H18" s="12"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -1404,23 +1442,20 @@
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
     </row>
-    <row r="19" spans="1:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="20" t="s">
+    <row r="19" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="34"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="22">
+      <c r="G19" s="33">
         <f>SUM(Sheet1!$G$3:$G$18)</f>
         <v>43.338999999999999</v>
       </c>
-      <c r="H19" s="23">
-        <f>SUBTOTAL(103,Sheet1!$H$3:$H$18)</f>
-        <v>3</v>
-      </c>
+      <c r="H19" s="24"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -1429,12 +1464,11 @@
       <c r="N19" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="B3:B8"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="B15:B18"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="H1:N1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F3" r:id="rId1" xr:uid="{26C41CE9-6DD4-417E-B327-9FEAF34153CA}"/>
